--- a/Result/profitability/1569.xlsx
+++ b/Result/profitability/1569.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.03875</v>
+        <v>-1.0325</v>
       </c>
       <c r="N2" t="n">
-        <v>4.11</v>
+        <v>4.32625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8787499999999999</v>
+        <v>-0.8762499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>5.09875</v>
+        <v>6.185</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.95</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6399999999999999</v>
+        <v>-0.5912499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>7.7425</v>
+        <v>8.397500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5037499999999999</v>
+        <v>-0.3362499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.66375</v>
+        <v>9.438749999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2249999999999999</v>
+        <v>-0.2237499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>10.45125</v>
+        <v>11.2325</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05250000000000007</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="N7" t="n">
-        <v>12.995</v>
+        <v>14.2825</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3762500000000001</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>17.5825</v>
+        <v>17.50125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>819</v>
+      </c>
+      <c r="D75" t="n">
+        <v>766</v>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-96</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-11.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-106</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-135</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.1675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2876712328767124</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6499999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09103641456582623</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5877192982456141</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>21.37931034482759</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
